--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(ns1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(ns1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_盖亚之心（无索菲亚线上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="457">
   <si>
     <t>ID</t>
   </si>
@@ -120,7 +120,10 @@
     <t>就在这时，一阵轻微的脚步声自培养罐后突兀地响起。先是一道阴影浮现，继而显现出一名男子的轮廓。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_gy(2)_80,1)</t>
+    <t>9 enhanced suspense tensions</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_gy(2)_80,1)&amp;unlockmusic(Music9)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=3</t>
@@ -387,6 +390,9 @@
     <t>这里，准确来说是整个医院，自始至终都是一场人为营造的梦境。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Gaiman; 层级=29</t>
   </si>
   <si>
@@ -417,6 +423,12 @@
     <t>荒诞至极，我们是身负任务来这里回收盖亚之心的特工，如果你试图以这种方式故弄玄虚，妨碍我们完成公务，它通常不会奏效。</t>
   </si>
   <si>
+    <t>4 enhanced leberch-spooky-piano</t>
+  </si>
+  <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music4)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Clark; 层级=32</t>
   </si>
   <si>
@@ -697,6 +709,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -747,6 +764,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -774,6 +796,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2881,21 +2908,21 @@
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2913,7 +2940,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2928,12 +2955,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2951,7 +2978,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2963,12 +2990,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="55.5" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2986,7 +3013,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3001,15 +3028,15 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -3024,7 +3051,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3039,15 +3066,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -3062,7 +3089,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3077,12 +3104,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3100,7 +3127,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3112,24 +3139,24 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3138,7 +3165,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3150,15 +3177,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3167,7 +3194,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3176,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3188,18 +3215,18 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3214,7 +3241,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3229,12 +3256,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3252,7 +3279,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3267,21 +3294,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3290,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3302,15 +3329,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="55.5" spans="1:12">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3319,7 +3346,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3328,7 +3355,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3340,24 +3367,24 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:12">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3366,7 +3393,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3378,15 +3405,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3395,7 +3422,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3404,7 +3431,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3419,21 +3446,21 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:12">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3442,7 +3469,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3457,12 +3484,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:12">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3471,7 +3498,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3480,7 +3507,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3492,15 +3519,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3533,21 +3560,21 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="90" spans="1:12">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3556,7 +3583,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3568,15 +3595,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3585,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3594,7 +3621,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3606,24 +3633,24 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:12">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3632,7 +3659,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3644,15 +3671,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3661,7 +3688,7 @@
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3670,7 +3697,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3682,18 +3709,18 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -3708,7 +3735,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3723,15 +3750,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3746,7 +3773,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3761,12 +3788,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="40.5" spans="1:12">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3784,7 +3811,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3799,21 +3826,21 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="55.5" spans="1:12">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3822,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3834,24 +3861,24 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3860,13 +3887,13 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -3875,21 +3902,21 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3898,7 +3925,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3910,15 +3937,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" ht="67.5" spans="1:12">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3936,7 +3963,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3951,21 +3978,21 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" ht="40.5" spans="1:12">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" ht="45" spans="1:12">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3974,27 +4001,27 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" ht="57" spans="1:12">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4003,7 +4030,7 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4012,7 +4039,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4024,24 +4051,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L35" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4050,7 +4077,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4062,15 +4089,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L36" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4079,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4088,7 +4115,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4100,15 +4127,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L37" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4126,7 +4153,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4141,12 +4168,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4164,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4179,21 +4206,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" ht="67.5" spans="1:12">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4202,7 +4229,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4214,15 +4241,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L40" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" ht="42" spans="1:12">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4231,7 +4258,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4240,7 +4267,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4252,15 +4279,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L41" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" ht="55.5" spans="1:12">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4278,7 +4305,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4293,12 +4320,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:12">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4316,7 +4343,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4331,15 +4358,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4354,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4369,12 +4396,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4392,7 +4419,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4407,12 +4434,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" ht="27" spans="1:12">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4430,7 +4457,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4445,21 +4472,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4468,7 +4495,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4480,24 +4507,24 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L47" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4506,7 +4533,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4521,21 +4548,21 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" ht="69" spans="1:12">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4544,7 +4571,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4559,12 +4586,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4573,7 +4600,7 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4582,7 +4609,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4597,21 +4624,21 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4620,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4635,21 +4662,21 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" ht="69" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4658,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4673,12 +4700,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4687,7 +4714,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4696,7 +4723,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4711,21 +4738,21 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" ht="55.5" spans="1:12">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4734,7 +4761,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4749,12 +4776,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" ht="58.5" spans="1:12">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4763,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4772,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4784,18 +4811,18 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L55" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4810,7 +4837,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4822,18 +4849,18 @@
         <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4848,7 +4875,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4863,12 +4890,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4886,7 +4913,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4898,24 +4925,24 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L58" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" ht="42" spans="1:12">
       <c r="A59" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -4924,7 +4951,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4936,15 +4963,15 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L59" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4953,7 +4980,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -4962,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4974,24 +5001,24 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L60" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5000,7 +5027,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5012,24 +5039,24 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L61" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5038,7 +5065,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5053,21 +5080,21 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5076,7 +5103,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5088,12 +5115,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" ht="67.5" spans="1:12">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5102,7 +5129,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5111,7 +5138,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5123,15 +5150,15 @@
         <v>15</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5149,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5164,12 +5191,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5199,15 +5226,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L66" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5231,21 +5258,21 @@
         <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="J67" t="s">
         <v>15</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="L67" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5269,30 +5296,30 @@
         <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="J68" t="s">
         <v>15</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L68" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" ht="150" spans="1:12">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5301,7 +5328,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5313,15 +5340,15 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L69" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5330,7 +5357,7 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5339,7 +5366,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5351,24 +5378,24 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5377,7 +5404,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5389,15 +5416,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" ht="30" spans="1:12">
       <c r="A72" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5406,7 +5433,7 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5415,7 +5442,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5430,21 +5457,21 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5453,7 +5480,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5468,12 +5495,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5482,7 +5509,7 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5491,7 +5518,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5503,15 +5530,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L74" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5529,7 +5556,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5544,15 +5571,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5567,7 +5594,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5582,12 +5609,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5605,7 +5632,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5620,12 +5647,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5643,7 +5670,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5658,12 +5685,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" ht="27" spans="1:12">
       <c r="A79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5681,7 +5708,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5696,12 +5723,12 @@
         <v>15</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="80" ht="27" spans="1:12">
       <c r="A80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5719,7 +5746,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5734,12 +5761,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5757,7 +5784,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5772,21 +5799,21 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -5795,7 +5822,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5807,15 +5834,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L82" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" ht="40.5" spans="1:12">
       <c r="A83" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5824,7 +5851,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -5833,7 +5860,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5845,24 +5872,24 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L83" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" ht="30" spans="1:12">
       <c r="A84" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -5871,7 +5898,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5883,15 +5910,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L84" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" ht="30" spans="1:12">
       <c r="A85" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5900,7 +5927,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -5909,7 +5936,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5921,10 +5948,10 @@
         <v>15</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L85" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5945,39 +5972,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" ht="43.5" spans="1:2">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5985,7 +6012,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -5993,7 +6020,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -6001,66 +6028,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B14" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -6082,616 +6109,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D6" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C7" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B8" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C8" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B9" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C9" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D9" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E9" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B10" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C11" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D11" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E11" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B13" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D13" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B14" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D14" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F14" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B15" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C15" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E15" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C16" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D16" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E16" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F16" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B17" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C17" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D17" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E17" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F17" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B18" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C18" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D18" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F18" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C19" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D19" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E19" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F19" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B20" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C20" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D20" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E20" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F20" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B21" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C21" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D21" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E21" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F21" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B22" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C22" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D22" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E22" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F22" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B23" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C23" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D23" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E23" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F23" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B24" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D24" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E24" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F24" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B25" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C25" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D25" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E25" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F25" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B26" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D26" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E26" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F26" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B27" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C27" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D27" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E27" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F27" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B28" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D28" t="s">
         <v>436</v>
       </c>
-      <c r="D28" t="s">
-        <v>432</v>
-      </c>
       <c r="E28" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B29" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C29" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D29" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E29" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F29" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B30" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C30" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D30" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E30" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F30" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C31" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D31" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(ns1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(ns1).xlsx
@@ -651,7 +651,7 @@
     <t>两个相似的声音在你耳边交错略过，盖曼的告诫，还有亚波伦辛辣的讥讽。一白一黑的影子在你意识里不断盘旋碰撞，渐渐勾勒这张阴谋大网的真实轮廓。</t>
   </si>
   <si>
-    <t>parallel(memoryoff();bgfade(bgfade(sntzm_gy(2)_66,1),1))</t>
+    <t>parallel(memoryoff();bgfade(sntzm_gy(2)_66,1))</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=58</t>
